--- a/www/download/COUNTRY.BRA.zdW16.xlsx
+++ b/www/download/COUNTRY.BRA.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>1.82714812301343</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>2.33425070551513</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>2.82848624060305</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>3.05822554856088</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>2.92042426547351</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>2.42366073086374</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>2.17532701290793</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>1.94705945334289</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1.83376547668029</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>1.99942818010536</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>1.7592253781161</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1.67282825887095</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>1.95306778037548</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>2.15608782030089</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.35352817682768</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>81.003</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>81.87</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>85.429</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>86.351</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.884</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>94.081</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>95.555</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>97.564</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>99.374</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>99.518</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>99.173</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>100.261</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>101.492</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>102.993</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>104.031</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>67.891</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>68.934</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>70.713</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>74.53</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>78.471</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>81.918</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>84.17</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>87.965</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>87.419</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>84.512</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>85.825</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>88.105</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>88.016</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>92.733</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>93.704</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>175462.81</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>177780.558</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>185774.53</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>187182.611</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>195734.938</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>200573.726</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>203337.135</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>207749.264</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>211668.081</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>212019.953</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>211757.907</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>214605.695</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>217748.762</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>220932.438</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>222764.588</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>147586.76</t>
+          <t>144895736826.753</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150219.519</t>
+          <t>140712925638.407</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>154195.149</t>
+          <t>145845374162.527</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>162195.703</t>
+          <t>150176604624.97</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>170243.617</t>
+          <t>157488013465.018</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>175636.448</t>
+          <t>161177759159.053</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>180026.749</t>
+          <t>158940962292.051</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>188347.258</t>
+          <t>160718024088.636</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>187052.339</t>
+          <t>166646620260.008</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>180756.587</t>
+          <t>158051172269.521</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>184158.57</t>
+          <t>162838034873.002</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>189584.217</t>
+          <t>164202509249.778</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>189252.988</t>
+          <t>162030849639.782</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>199590.815</t>
+          <t>164479979162.365</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>201311.206</t>
+          <t>165354943293.498</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>32258197479.4402</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30187019125.0107</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30554667866.548</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30975231594.4169</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>32194405855.6949</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>34104042140.9031</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>35048040464.4393</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>36128288004.7921</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>37774199933.4172</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>38405208311.453</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>40277212529.6407</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>40864301389.457</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>40448067862.7557</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>41162061023.9373</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>41894644026.657</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6605294.68841741</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7341509.59455444</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7758862.12321887</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6988214.76866022</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6241805.34330438</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5126298.73521813</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4273873.95723342</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3401129.46080701</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2813894.16105437</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2914734.60543168</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2187624.37738038</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1859749.6804713</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1929404.55301748</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1955422.08690971</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1987480.83891765</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>788983.836986034</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>766611.72813318</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>803794.329182758</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>891492.798969579</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1031750.9512521</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1133998.29769516</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1176553.56843378</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1348028.35253228</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1511780.43493736</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1361388.69007389</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1540951.92063785</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1638986.40187177</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1610260.55645677</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1639032.1464601</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1670289.2121154</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1314398.4627657</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1257763.98919715</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1313229.65075114</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1472172.48951633</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1701349.53266848</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1880651.94982977</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1959727.70284529</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2222939.16428745</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2513909.62497538</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2178951.00493152</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2480274.46065065</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2666684.83507392</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2570407.22723283</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2594130.06187361</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2617034.11689383</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.57517070177479</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.97629522073411</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4.04653330461551</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>4.23630315743094</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4.28798753929746</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4.15001850145347</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4.13657102121472</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4.21329042701988</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3.9518544225876</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3.70656442048501</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3.57227693859088</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.63936028645562</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3.67891293700738</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3.84890236385224</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3.80517762298943</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.82714812301343</t>
+          <t>475.149864019272</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33425070551513</t>
+          <t>437.912080925944</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.82848624060305</t>
+          <t>432.096897704972</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05822554856088</t>
+          <t>415.605894649865</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.92042426547351</t>
+          <t>410.272801922038</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.42366073086374</t>
+          <t>416.319241717177</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.17532701290793</t>
+          <t>416.393837787478</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.94705945334289</t>
+          <t>410.711121571218</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.83376547668029</t>
+          <t>432.103571218819</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.99942818010536</t>
+          <t>454.436358813347</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.7592253781161</t>
+          <t>469.296603636719</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1.67282825887095</t>
+          <t>463.815352881577</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.95306778037548</t>
+          <t>459.552389165731</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.15608782030089</t>
+          <t>443.877517937235</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.35352817682768</t>
+          <t>447.096885204512</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>-1509837158.95372</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>-4482589341.97628</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>-5455131498.86566</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-4737920506.1392</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>-6048209826.83338</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>-3847824503.24497</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-596997467.6994</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>383192091.787095</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>1430962188.31042</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>659962828.455901</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>3255402897.20871</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>6362491882.80133</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>4730972843.96614</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3446676440.27199</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>2501344723.40933</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>-772775207.202687</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>-3952647018.87215</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>-5156789526.6911</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>-4406893722.46856</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>-5733193278.66738</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>-3332047007.83138</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>-12352168.0391284</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>1306085227.49517</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>2456575219.74628</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>1880502589.82992</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>5176329285.16361</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>8470025412.92752</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>7100103245.85004</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>6251460956.01443</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>4821274552.71873</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.209</t>
+          <t>-737061951.751029</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>-529942323.104129</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>-298341972.174561</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>-331026783.670637</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.189</t>
+          <t>-315016548.166003</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>-515777495.413593</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.085</t>
+          <t>-584645299.660272</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.733</t>
+          <t>-922893135.70808</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>-1025613031.43586</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.658</t>
+          <t>-1220539761.37402</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>5.957</t>
+          <t>-1920926387.95489</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>6.997</t>
+          <t>-2107533530.12619</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.902</t>
+          <t>-2369130401.88389</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>6.936</t>
+          <t>-2804784515.74244</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7.455</t>
+          <t>-2319929829.30939</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2173.89173681325</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>2179.1797954135</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2180.59138508918</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>2176.238458402</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.228</t>
+          <t>2169.51746427639</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>2144.05179735454</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>2138.83652059154</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2141.15635835783</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.037</t>
+          <t>2139.71398015581</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.872</t>
+          <t>2138.83399776566</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.752</t>
+          <t>2145.7540381672</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>2151.80652840719</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.207</t>
+          <t>2150.20561890019</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.217</t>
+          <t>2152.31874598673</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>2148.37994809299</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>2166.11981962571</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>2171.49976709589</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>2174.61926974621</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>2167.69115225718</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>2153.6888299838</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>2131.92726739207</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>2127.94937976037</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>2129.37200436221</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2130.01960648599</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>2130.47328629532</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>2135.22921277425</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.223</t>
+          <t>2140.4794196597</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2.092</t>
+          <t>2145.47855809279</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2145.11951226953</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2.072</t>
+          <t>2141.31939734814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>64412.4060268726</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>67952.8643989899</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>73651.7537576181</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>85277.5400451185</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>110917.101989436</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>136520.772125384</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>159213.776013615</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>186202.864348366</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>229517.314516081</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>180891.688294451</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>237189.636258414</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>299972.304316578</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>288507.150359956</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>287593.573102253</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>270262.888633861</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12486205546.43</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15929496331.1909</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>18921038839.0077</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19926618696.4023</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>22153556713.3094</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>20305461694.4253</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>18711253804.4201</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>17720479442.7259</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>17329448047.6481</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15701160887.4129</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>14662946461.4703</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>15098384201.0646</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15404008448.8673</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>15859612910.8357</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>16281921597.7523</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>71827.0372404663</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70789.737170807</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>61885.3254382245</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>68617.2449189643</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>82732.2716240755</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>100226.647752191</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>122560.410162537</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>158010.360920663</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>219320.764175047</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>177460.526015383</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>247128.187048731</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>305666.612551388</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>306948.122165511</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>326863.637005248</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>317343.401152447</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>175462.81</t>
+          <t>11990355461.7684</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>177780.558</t>
+          <t>11850681572.4959</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>185774.53</t>
+          <t>11780619020.475</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>187182.611</t>
+          <t>12939395630.4354</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>195734.938</t>
+          <t>12637940882.1301</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>200573.726</t>
+          <t>12407968980.1748</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>203337.135</t>
+          <t>14402595738.6538</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>207749.264</t>
+          <t>15655675913.4975</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>211668.081</t>
+          <t>17987421983.92</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>212019.953</t>
+          <t>16068954377.2028</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>211757.907</t>
+          <t>18672759941.0216</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>214605.695</t>
+          <t>21870073484.3535</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>217748.762</t>
+          <t>21468991817.9491</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>220932.438</t>
+          <t>22175389897.8407</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>222764.588</t>
+          <t>22189968391.6775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>147586.76</t>
+          <t>-7414.63121359367</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>150219.519</t>
+          <t>-2836.87277181708</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>154195.149</t>
+          <t>11766.4283193936</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>162195.703</t>
+          <t>16660.2951261543</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>170243.617</t>
+          <t>28184.8303653603</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>175636.448</t>
+          <t>36294.1243731925</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>180026.749</t>
+          <t>36653.3658510785</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>188347.258</t>
+          <t>28192.5034277023</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>187052.339</t>
+          <t>10196.550341034</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>180756.587</t>
+          <t>3431.16227906843</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>184158.57</t>
+          <t>-9938.55079031728</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>189584.217</t>
+          <t>-5694.30823481034</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>189252.988</t>
+          <t>-18440.9718055543</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>199590.815</t>
+          <t>-39270.0639029952</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>201311.206</t>
+          <t>-47080.5125185863</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>160614.011</t>
+          <t>495850084.661664</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>156906.105</t>
+          <t>4078814758.69505</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>163445.867</t>
+          <t>7140419818.53273</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>169352.866</t>
+          <t>6987223065.96693</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>176542.243</t>
+          <t>9515615831.17934</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>181427.556</t>
+          <t>7897492714.25049</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>178225.115</t>
+          <t>4308658065.76632</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>179518.727</t>
+          <t>2064803529.22841</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>187531.82</t>
+          <t>-657973936.271867</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>179676.585</t>
+          <t>-367793489.78985</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>184778.199</t>
+          <t>-4009813479.5513</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>186320.706</t>
+          <t>-6771689283.28895</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>184855.52</t>
+          <t>-6064983369.08183</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>187364.254</t>
+          <t>-6315776987.00501</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>165354.943</t>
+          <t>-5908046793.92517</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>255455.774777055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>212330.705237634</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>204297.720771646</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>227075.20819658</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>280770.358973347</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.898</t>
+          <t>350128.310474986</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>417487.18075335</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>528077.958443412</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.539</t>
+          <t>641281.434744514</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>630659.387334604</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>830218.810144</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.701</t>
+          <t>991999.02876</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>909308.94313</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.644</t>
+          <t>911068.176429</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2.617</t>
+          <t>880908.596136649</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>86975.447</t>
+          <t>0.129940394789282</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>85765.04</t>
+          <t>0.126208479769339</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>89268.229</t>
+          <t>0.126823165418658</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>90941.355</t>
+          <t>0.135511313001388</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>95505.6</t>
+          <t>0.140972371321195</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>97187.204</t>
+          <t>0.146632368341698</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>95422.724</t>
+          <t>0.156284169152822</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>97462.16</t>
+          <t>0.165822743384003</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>100215.655</t>
+          <t>0.159903904846648</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>98748.929</t>
+          <t>0.147535764864252</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>101168.474</t>
+          <t>0.146213646221708</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>100921.442</t>
+          <t>0.145453042753171</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>101506.051</t>
+          <t>0.133415543874526</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>103922.304</t>
+          <t>0.135380975694213</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>105535.719</t>
+          <t>0.124732004961867</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>261521.620925861</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>225368.877482007</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>207862.748106387</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>220064.149642965</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>262729.814033818</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>351578.78311947</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>436350.595752985</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>557819.431458893</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>681889.6530067</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>701113.876565657</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>919830.978221856</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1103987.217297</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>1054164.13047212</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1070145.18482647</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1069813.78448037</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>35826.052</t>
+          <t>286764.527694148</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>33691.691</t>
+          <t>246799.864308916</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>34289.44</t>
+          <t>226901.661516056</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>34877.084</t>
+          <t>236855.339605692</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>36012.595</t>
+          <t>281625.76394464</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>38249.016</t>
+          <t>376041.045922673</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>39156.271</t>
+          <t>466335.084382145</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>40126.535</t>
+          <t>585169.338135821</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>42223.399</t>
+          <t>723188.424727551</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>43389.734</t>
+          <t>751612.297771597</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>45426.496</t>
+          <t>1006835.71333107</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>46083.629</t>
+          <t>1205162.08862886</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>45783.831</t>
+          <t>1171297.73597218</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>46489.779</t>
+          <t>1166517.37287097</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>41894.644</t>
+          <t>1142066.87338497</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>311.95</t>
+          <t>2208829.95626249</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>345.87</t>
+          <t>1917765.26549577</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>349.69</t>
+          <t>1851935.52144764</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>365.05</t>
+          <t>1896832.45194088</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>372.73</t>
+          <t>2188885.36879494</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>359.19</t>
+          <t>2742637.2953084</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>359.76</t>
+          <t>3085499.84878598</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>369.38</t>
+          <t>3733034.77112992</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>343.01</t>
+          <t>4483591.68792562</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>316.59</t>
+          <t>4657916.79617169</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>305.4</t>
+          <t>5956607.76078443</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>311.39</t>
+          <t>6997070.08039855</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>313.36</t>
+          <t>6902478.83828462</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>329.32</t>
+          <t>6935785.39069556</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>380.52</t>
+          <t>7454852.05712726</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>7.382</t>
+          <t>678321.778891792</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.266</t>
+          <t>681935.382811492</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>8.787</t>
+          <t>686478.278418203</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7.949</t>
+          <t>680043.501327831</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>713947.537031798</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.814</t>
+          <t>736666.982652353</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.836</t>
+          <t>764365.536578361</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>797544.979783614</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.199</t>
+          <t>855096.762608292</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>882328.952710944</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.549</t>
+          <t>969407.411878416</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>1025250.75335579</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>1079508.36715359</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>1097663.24266106</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.987</t>
+          <t>1109477.44219704</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>617070.843151975</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>621627.031670966</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>629113.006047609</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>633899.545655779</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>669531.520477917</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>690564.163949645</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>715644.321808174</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>760692.485858496</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>807873.22672538</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>823577.313632058</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>885637.007608958</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>940562.763527484</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>974133.831196351</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1009581.16686428</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1039174.4206431</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>287016.236539141</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>242038.238712664</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>234868.324981242</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>257042.25610615</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>308572.360989292</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>402159.402113339</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>482214.780288676</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>619022.066896638</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>716943.818637279</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>687209.317197237</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>870937.339816817</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1017745.13355114</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>920897.968292148</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>938973.393398031</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>929858.643779579</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>147586760000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150219519000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>154195149000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>162195703000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>170243617000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>175636448000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>180026749000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>188347258000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>187052339000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>180756587000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>184158570000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>189584217000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>189252988000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>199590815000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>201311206000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>175462810262.691</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>177780557813.654</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>185774529698.711</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>187182610836.086</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>195734938152.806</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>200573725591.732</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>203337135024.83</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>207749264495.325</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>211668080600.449</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>212019952627.155</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>211757906646.478</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>214605695250.268</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>217748761779.933</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>220932437650.183</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>222764587515.086</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>86975447433.1493</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>85765040198.9891</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>89268228616.6197</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>90941355411.9926</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>95505599868.4065</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>97187203899.8127</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>95422724332.3174</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>97462160330.3724</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>100215655151.081</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>98748929137.7656</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>101168474123.069</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>100921442336.904</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>101506050613.234</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>103922304150.585</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>105535719297.727</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>81003280</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>81869941</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>85428531</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>86351144</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>90883574</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>94080942</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>95555438</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>97563631</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>99373771</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>99517771</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>99173384</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>100260574</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>101491931</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>102993067</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>104031462</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>67890575</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>68933972</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>70712537</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>74530299</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>78470729</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>81918006</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>84170411</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>87965205</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>87419319</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>84511742</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>85824641</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>88104676</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>88016228</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>92732926</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>93703726</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>175462810262.691</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>177780557813.654</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>185774529698.711</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>187182610836.086</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>195734938152.806</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>200573725591.732</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>203337135024.83</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>207749264495.325</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>211668080600.449</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>212019952627.155</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>211757906646.478</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>214605695250.268</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>217748761779.933</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>220932437650.183</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>222764587515.086</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>147586760000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>150219519000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>154195149000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>162195703000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>170243617000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>175636448000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>180026749000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>188347258000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>187052339000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>180756587000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>184158570000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>189584217000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>189252988000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>199590815000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>201311206000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1150451.4285624</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>993535.107520598</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>939685.511931887</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1020845.03736714</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1227682.98815445</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1634664.59418755</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1985416.78351458</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2490215.52872017</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3036708.36723138</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2872494.31961956</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>3751500.56552</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4445219.04552</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4206527.84251</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4216646.886183</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4103501.78349504</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>573780.768611696</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>488838.113303252</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>461769.989325666</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>493897.597673764</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>590198.131782251</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>778200.446798215</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>948549.86007381</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1204191.40965481</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1440132.25699798</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1438821.62547184</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1877773.048032</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2222907.22218</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2092195.693</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2105490.766269</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2071925.52268817</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4450508.39547451</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4650382.64563363</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4983700.77616338</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4970140.62597645</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5132802.82447908</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4992787.68364763</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4825973.79075239</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4945170.09843315</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>5129817.24894937</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>5553352.81377693</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>5735175.69528026</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>5907330.43175506</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>6309976.53229298</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>6474958.94578575</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>7180399.25740998</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
